--- a/Data/EXCEL/Transfer/salemon/202208/6550-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6550-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AA198D6-F9C9-48F7-9EC5-5522405545F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{996AB066-93E6-4EB6-8AF4-8520F3C30938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6550-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,24 +1226,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="2" width="9.375" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="9.75" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
-    <col min="7" max="7" width="9.75" customWidth="1"/>
-    <col min="8" max="8" width="11.25" customWidth="1"/>
-    <col min="9" max="10" width="9.75" customWidth="1"/>
-    <col min="11" max="11" width="11.25" customWidth="1"/>
-    <col min="12" max="12" width="9.375" customWidth="1"/>
-    <col min="13" max="13" width="11.25" customWidth="1"/>
-    <col min="14" max="15" width="9.75" customWidth="1"/>
-    <col min="16" max="16" width="11.25" customWidth="1"/>
-    <col min="17" max="17" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="3" width="13.875" customWidth="1"/>
+    <col min="4" max="4" width="13.25" customWidth="1"/>
+    <col min="5" max="5" width="13.875" customWidth="1"/>
+    <col min="6" max="6" width="13.25" customWidth="1"/>
+    <col min="7" max="7" width="13.875" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
+    <col min="9" max="10" width="13.875" customWidth="1"/>
+    <col min="11" max="11" width="15.875" customWidth="1"/>
+    <col min="12" max="12" width="13.25" customWidth="1"/>
+    <col min="13" max="13" width="15.875" customWidth="1"/>
+    <col min="14" max="15" width="13.875" customWidth="1"/>
+    <col min="16" max="16" width="15.875" customWidth="1"/>
+    <col min="17" max="17" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1388,166 +1395,166 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>115</v>
+        <v>126.5</v>
       </c>
       <c r="C5" s="7">
-        <v>126.5</v>
+        <v>183.5</v>
       </c>
       <c r="D5" s="7">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="E5" s="7">
-        <v>107.5</v>
+        <v>112</v>
       </c>
       <c r="F5" s="8">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="G5" s="8">
-        <v>9.52</v>
+        <v>45.06</v>
       </c>
       <c r="H5" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I5" s="10">
-        <v>-54.6</v>
+        <v>-72.099999999999994</v>
       </c>
       <c r="J5" s="10">
-        <v>-52</v>
+        <v>-94</v>
       </c>
       <c r="K5" s="9">
-        <v>5.4800000000000001E-2</v>
+        <v>5.5599999999999997E-2</v>
       </c>
       <c r="L5" s="10">
-        <v>-32</v>
+        <v>-40.299999999999997</v>
       </c>
       <c r="M5" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="N5" s="10">
-        <v>-54.6</v>
+        <v>-72.099999999999994</v>
       </c>
       <c r="O5" s="10">
-        <v>-52</v>
+        <v>-94</v>
       </c>
       <c r="P5" s="9">
-        <v>5.4800000000000001E-2</v>
+        <v>5.5599999999999997E-2</v>
       </c>
       <c r="Q5" s="10">
-        <v>-32</v>
+        <v>-40.299999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>94.1</v>
+        <v>115</v>
       </c>
       <c r="C6" s="7">
-        <v>115.5</v>
+        <v>126.5</v>
       </c>
       <c r="D6" s="7">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E6" s="7">
-        <v>86.1</v>
+        <v>107.5</v>
       </c>
       <c r="F6" s="8">
-        <v>33.5</v>
+        <v>11</v>
       </c>
       <c r="G6" s="8">
-        <v>40.85</v>
+        <v>9.52</v>
       </c>
       <c r="H6" s="9">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0.16</v>
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="I6" s="10">
+        <v>-54.6</v>
       </c>
       <c r="J6" s="10">
-        <v>-46.9</v>
+        <v>-52</v>
       </c>
       <c r="K6" s="9">
-        <v>5.21E-2</v>
+        <v>5.4800000000000001E-2</v>
       </c>
       <c r="L6" s="10">
-        <v>-30.5</v>
+        <v>-32</v>
       </c>
       <c r="M6" s="9">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="N6" s="8">
-        <v>0.16</v>
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="N6" s="10">
+        <v>-54.6</v>
       </c>
       <c r="O6" s="10">
-        <v>-46.9</v>
+        <v>-52</v>
       </c>
       <c r="P6" s="9">
-        <v>5.21E-2</v>
+        <v>5.4800000000000001E-2</v>
       </c>
       <c r="Q6" s="10">
-        <v>-30.5</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>17</v>
+        <v>44713</v>
+      </c>
+      <c r="B7" s="7">
+        <v>94.1</v>
+      </c>
+      <c r="C7" s="7">
+        <v>115.5</v>
+      </c>
+      <c r="D7" s="7">
+        <v>122</v>
+      </c>
+      <c r="E7" s="7">
+        <v>86.1</v>
+      </c>
+      <c r="F7" s="8">
+        <v>33.5</v>
+      </c>
+      <c r="G7" s="8">
+        <v>40.85</v>
       </c>
       <c r="H7" s="9">
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="I7" s="8">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
       <c r="J7" s="10">
-        <v>-80.099999999999994</v>
+        <v>-46.9</v>
       </c>
       <c r="K7" s="9">
-        <v>4.6300000000000001E-2</v>
+        <v>5.21E-2</v>
       </c>
       <c r="L7" s="10">
-        <v>-27.4</v>
+        <v>-30.5</v>
       </c>
       <c r="M7" s="9">
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="N7" s="8">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
       <c r="O7" s="10">
-        <v>-80.099999999999994</v>
+        <v>-46.9</v>
       </c>
       <c r="P7" s="9">
-        <v>4.6300000000000001E-2</v>
+        <v>5.21E-2</v>
       </c>
       <c r="Q7" s="10">
-        <v>-27.4</v>
+        <v>-30.5</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>17</v>
@@ -1570,37 +1577,37 @@
       <c r="H8" s="9">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="I8" s="10">
-        <v>-75.599999999999994</v>
+      <c r="I8" s="8">
+        <v>0.33</v>
       </c>
       <c r="J8" s="10">
-        <v>-15.5</v>
+        <v>-80.099999999999994</v>
       </c>
       <c r="K8" s="9">
-        <v>4.0399999999999998E-2</v>
-      </c>
-      <c r="L8" s="8">
-        <v>18.5</v>
+        <v>4.6300000000000001E-2</v>
+      </c>
+      <c r="L8" s="10">
+        <v>-27.4</v>
       </c>
       <c r="M8" s="9">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="N8" s="10">
-        <v>-75.599999999999994</v>
+      <c r="N8" s="8">
+        <v>0.33</v>
       </c>
       <c r="O8" s="10">
-        <v>-15.5</v>
+        <v>-80.099999999999994</v>
       </c>
       <c r="P8" s="9">
-        <v>4.0399999999999998E-2</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>18.5</v>
+        <v>4.6300000000000001E-2</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>-27.4</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>17</v>
@@ -1621,39 +1628,39 @@
         <v>17</v>
       </c>
       <c r="H9" s="9">
-        <v>2.4199999999999999E-2</v>
-      </c>
-      <c r="I9" s="8">
-        <v>291.60000000000002</v>
-      </c>
-      <c r="J9" s="8">
-        <v>30</v>
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="I9" s="10">
+        <v>-75.599999999999994</v>
+      </c>
+      <c r="J9" s="10">
+        <v>-15.5</v>
       </c>
       <c r="K9" s="9">
-        <v>3.4500000000000003E-2</v>
+        <v>4.0399999999999998E-2</v>
       </c>
       <c r="L9" s="8">
-        <v>27.2</v>
+        <v>18.5</v>
       </c>
       <c r="M9" s="9">
-        <v>2.4199999999999999E-2</v>
-      </c>
-      <c r="N9" s="8">
-        <v>291.60000000000002</v>
-      </c>
-      <c r="O9" s="8">
-        <v>30</v>
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="N9" s="10">
+        <v>-75.599999999999994</v>
+      </c>
+      <c r="O9" s="10">
+        <v>-15.5</v>
       </c>
       <c r="P9" s="9">
-        <v>3.4500000000000003E-2</v>
+        <v>4.0399999999999998E-2</v>
       </c>
       <c r="Q9" s="8">
-        <v>27.2</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>17</v>
@@ -1674,39 +1681,39 @@
         <v>17</v>
       </c>
       <c r="H10" s="9">
-        <v>6.1999999999999998E-3</v>
+        <v>2.4199999999999999E-2</v>
       </c>
       <c r="I10" s="8">
-        <v>48.7</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="J10" s="8">
-        <v>45.2</v>
+        <v>30</v>
       </c>
       <c r="K10" s="9">
-        <v>1.03E-2</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="L10" s="8">
-        <v>21.3</v>
+        <v>27.2</v>
       </c>
       <c r="M10" s="9">
-        <v>6.1999999999999998E-3</v>
+        <v>2.4199999999999999E-2</v>
       </c>
       <c r="N10" s="8">
-        <v>48.7</v>
+        <v>291.60000000000002</v>
       </c>
       <c r="O10" s="8">
-        <v>45.2</v>
+        <v>30</v>
       </c>
       <c r="P10" s="9">
-        <v>1.03E-2</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="Q10" s="8">
-        <v>21.3</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>17</v>
@@ -1727,39 +1734,39 @@
         <v>17</v>
       </c>
       <c r="H11" s="9">
-        <v>4.1999999999999997E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="I11" s="8">
-        <v>49.3</v>
-      </c>
-      <c r="J11" s="10">
-        <v>-2.58</v>
+        <v>48.7</v>
+      </c>
+      <c r="J11" s="8">
+        <v>45.2</v>
       </c>
       <c r="K11" s="9">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="L11" s="10">
-        <v>-2.58</v>
+        <v>1.03E-2</v>
+      </c>
+      <c r="L11" s="8">
+        <v>21.3</v>
       </c>
       <c r="M11" s="9">
-        <v>4.1999999999999997E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="N11" s="8">
-        <v>49.3</v>
-      </c>
-      <c r="O11" s="10">
-        <v>-2.58</v>
+        <v>48.7</v>
+      </c>
+      <c r="O11" s="8">
+        <v>45.2</v>
       </c>
       <c r="P11" s="9">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>-2.58</v>
+        <v>1.03E-2</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>21.3</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>17</v>
@@ -1780,39 +1787,39 @@
         <v>17</v>
       </c>
       <c r="H12" s="9">
-        <v>2.8E-3</v>
-      </c>
-      <c r="I12" s="10">
-        <v>-94</v>
-      </c>
-      <c r="J12" s="8">
-        <v>54.4</v>
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="I12" s="8">
+        <v>49.3</v>
+      </c>
+      <c r="J12" s="10">
+        <v>-2.58</v>
       </c>
       <c r="K12" s="9">
-        <v>0.151</v>
-      </c>
-      <c r="L12" s="8">
-        <v>60.2</v>
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="L12" s="10">
+        <v>-2.58</v>
       </c>
       <c r="M12" s="9">
-        <v>2.8E-3</v>
-      </c>
-      <c r="N12" s="10">
-        <v>-94</v>
-      </c>
-      <c r="O12" s="8">
-        <v>54.4</v>
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="N12" s="8">
+        <v>49.3</v>
+      </c>
+      <c r="O12" s="10">
+        <v>-2.58</v>
       </c>
       <c r="P12" s="9">
-        <v>0.151</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>60.2</v>
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1833,39 +1840,39 @@
         <v>17</v>
       </c>
       <c r="H13" s="9">
-        <v>4.6800000000000001E-2</v>
-      </c>
-      <c r="I13" s="8">
-        <v>736.3</v>
+        <v>2.8E-3</v>
+      </c>
+      <c r="I13" s="10">
+        <v>-94</v>
       </c>
       <c r="J13" s="8">
-        <v>116.3</v>
+        <v>54.4</v>
       </c>
       <c r="K13" s="9">
-        <v>0.14799999999999999</v>
+        <v>0.151</v>
       </c>
       <c r="L13" s="8">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
       <c r="M13" s="9">
-        <v>4.6800000000000001E-2</v>
-      </c>
-      <c r="N13" s="8">
-        <v>736.3</v>
+        <v>2.8E-3</v>
+      </c>
+      <c r="N13" s="10">
+        <v>-94</v>
       </c>
       <c r="O13" s="8">
-        <v>116.3</v>
+        <v>54.4</v>
       </c>
       <c r="P13" s="9">
-        <v>0.14799999999999999</v>
+        <v>0.151</v>
       </c>
       <c r="Q13" s="8">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
@@ -1886,39 +1893,39 @@
         <v>17</v>
       </c>
       <c r="H14" s="9">
-        <v>5.5999999999999999E-3</v>
+        <v>4.6800000000000001E-2</v>
       </c>
       <c r="I14" s="8">
-        <v>168.8</v>
-      </c>
-      <c r="J14" s="10">
-        <v>-64.8</v>
+        <v>736.3</v>
+      </c>
+      <c r="J14" s="8">
+        <v>116.3</v>
       </c>
       <c r="K14" s="9">
-        <v>0.10100000000000001</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="L14" s="8">
-        <v>42.5</v>
+        <v>60.3</v>
       </c>
       <c r="M14" s="9">
-        <v>5.5999999999999999E-3</v>
+        <v>4.6800000000000001E-2</v>
       </c>
       <c r="N14" s="8">
-        <v>168.8</v>
-      </c>
-      <c r="O14" s="10">
-        <v>-64.8</v>
+        <v>736.3</v>
+      </c>
+      <c r="O14" s="8">
+        <v>116.3</v>
       </c>
       <c r="P14" s="9">
-        <v>0.10100000000000001</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="Q14" s="8">
-        <v>42.5</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>17</v>
@@ -1939,39 +1946,39 @@
         <v>17</v>
       </c>
       <c r="H15" s="9">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="I15" s="10">
-        <v>-83.3</v>
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="I15" s="8">
+        <v>168.8</v>
       </c>
       <c r="J15" s="10">
-        <v>-89.6</v>
+        <v>-64.8</v>
       </c>
       <c r="K15" s="9">
-        <v>9.5200000000000007E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="L15" s="8">
-        <v>73.599999999999994</v>
+        <v>42.5</v>
       </c>
       <c r="M15" s="9">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="N15" s="10">
-        <v>-83.3</v>
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="N15" s="8">
+        <v>168.8</v>
       </c>
       <c r="O15" s="10">
-        <v>-89.6</v>
+        <v>-64.8</v>
       </c>
       <c r="P15" s="9">
-        <v>9.5200000000000007E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="Q15" s="8">
-        <v>73.599999999999994</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
@@ -1992,39 +1999,39 @@
         <v>17</v>
       </c>
       <c r="H16" s="9">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="I16" s="8">
-        <v>123</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>17</v>
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="I16" s="10">
+        <v>-83.3</v>
+      </c>
+      <c r="J16" s="10">
+        <v>-89.6</v>
       </c>
       <c r="K16" s="9">
-        <v>9.3100000000000002E-2</v>
+        <v>9.5200000000000007E-2</v>
       </c>
       <c r="L16" s="8">
-        <v>168</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="M16" s="9">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="N16" s="8">
-        <v>123</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>17</v>
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="N16" s="10">
+        <v>-83.3</v>
+      </c>
+      <c r="O16" s="10">
+        <v>-89.6</v>
       </c>
       <c r="P16" s="9">
-        <v>9.3100000000000002E-2</v>
+        <v>9.5200000000000007E-2</v>
       </c>
       <c r="Q16" s="8">
-        <v>168</v>
+        <v>73.599999999999994</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>17</v>
@@ -2045,39 +2052,39 @@
         <v>17</v>
       </c>
       <c r="H17" s="9">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="I17" s="10">
-        <v>-49.9</v>
-      </c>
-      <c r="J17" s="10">
-        <v>-83.9</v>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="I17" s="8">
+        <v>123</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K17" s="9">
-        <v>8.0600000000000005E-2</v>
+        <v>9.3100000000000002E-2</v>
       </c>
       <c r="L17" s="8">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="M17" s="9">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="N17" s="10">
-        <v>-49.9</v>
-      </c>
-      <c r="O17" s="10">
-        <v>-83.9</v>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="N17" s="8">
+        <v>123</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P17" s="9">
-        <v>8.0600000000000005E-2</v>
+        <v>9.3100000000000002E-2</v>
       </c>
       <c r="Q17" s="8">
-        <v>132</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>17</v>
@@ -2098,39 +2105,39 @@
         <v>17</v>
       </c>
       <c r="H18" s="9">
-        <v>1.12E-2</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="I18" s="10">
-        <v>-62.4</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>17</v>
+        <v>-49.9</v>
+      </c>
+      <c r="J18" s="10">
+        <v>-83.9</v>
       </c>
       <c r="K18" s="9">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>17</v>
+        <v>8.0600000000000005E-2</v>
+      </c>
+      <c r="L18" s="8">
+        <v>132</v>
       </c>
       <c r="M18" s="9">
-        <v>1.12E-2</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="N18" s="10">
-        <v>-62.4</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>17</v>
+        <v>-49.9</v>
+      </c>
+      <c r="O18" s="10">
+        <v>-83.9</v>
       </c>
       <c r="P18" s="9">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>17</v>
+        <v>8.0600000000000005E-2</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>17</v>
@@ -2151,31 +2158,31 @@
         <v>17</v>
       </c>
       <c r="H19" s="9">
-        <v>2.9700000000000001E-2</v>
-      </c>
-      <c r="I19" s="8">
-        <v>325.89999999999998</v>
+        <v>1.12E-2</v>
+      </c>
+      <c r="I19" s="10">
+        <v>-62.4</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K19" s="9">
-        <v>6.3799999999999996E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M19" s="9">
-        <v>2.9700000000000001E-2</v>
-      </c>
-      <c r="N19" s="8">
-        <v>325.89999999999998</v>
+        <v>1.12E-2</v>
+      </c>
+      <c r="N19" s="10">
+        <v>-62.4</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P19" s="9">
-        <v>6.3799999999999996E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="Q19" s="9" t="s">
         <v>17</v>
@@ -2183,7 +2190,7 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>17</v>
@@ -2204,31 +2211,31 @@
         <v>17</v>
       </c>
       <c r="H20" s="9">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="I20" s="10">
-        <v>-62.4</v>
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="I20" s="8">
+        <v>325.89999999999998</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K20" s="9">
-        <v>3.4099999999999998E-2</v>
+        <v>6.3799999999999996E-2</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M20" s="9">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="N20" s="10">
-        <v>-62.4</v>
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="N20" s="8">
+        <v>325.89999999999998</v>
       </c>
       <c r="O20" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P20" s="9">
-        <v>3.4099999999999998E-2</v>
+        <v>6.3799999999999996E-2</v>
       </c>
       <c r="Q20" s="9" t="s">
         <v>17</v>
@@ -2236,7 +2243,7 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>17</v>
@@ -2257,31 +2264,31 @@
         <v>17</v>
       </c>
       <c r="H21" s="9">
-        <v>1.8599999999999998E-2</v>
-      </c>
-      <c r="I21" s="8">
-        <v>337.4</v>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I21" s="10">
+        <v>-62.4</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K21" s="9">
-        <v>2.7099999999999999E-2</v>
+        <v>3.4099999999999998E-2</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M21" s="9">
-        <v>1.8599999999999998E-2</v>
-      </c>
-      <c r="N21" s="8">
-        <v>337.4</v>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="N21" s="10">
+        <v>-62.4</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P21" s="9">
-        <v>2.7099999999999999E-2</v>
+        <v>3.4099999999999998E-2</v>
       </c>
       <c r="Q21" s="9" t="s">
         <v>17</v>
@@ -2289,7 +2296,7 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>17</v>
@@ -2310,31 +2317,31 @@
         <v>17</v>
       </c>
       <c r="H22" s="9">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="I22" s="10">
-        <v>-0.23</v>
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="I22" s="8">
+        <v>337.4</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K22" s="9">
-        <v>8.5000000000000006E-3</v>
+        <v>2.7099999999999999E-2</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M22" s="9">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="N22" s="10">
-        <v>-0.23</v>
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="N22" s="8">
+        <v>337.4</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P22" s="9">
-        <v>8.5000000000000006E-3</v>
+        <v>2.7099999999999999E-2</v>
       </c>
       <c r="Q22" s="9" t="s">
         <v>17</v>
@@ -2342,7 +2349,7 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>17</v>
@@ -2363,31 +2370,31 @@
         <v>17</v>
       </c>
       <c r="H23" s="9">
-        <v>4.3E-3</v>
-      </c>
-      <c r="I23" s="8">
-        <v>136.69999999999999</v>
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="I23" s="10">
+        <v>-0.23</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K23" s="9">
-        <v>4.3E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="L23" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M23" s="9">
-        <v>4.3E-3</v>
-      </c>
-      <c r="N23" s="8">
-        <v>136.69999999999999</v>
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="N23" s="10">
+        <v>-0.23</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P23" s="9">
-        <v>4.3E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="Q23" s="9" t="s">
         <v>17</v>
@@ -2395,7 +2402,7 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>17</v>
@@ -2416,31 +2423,31 @@
         <v>17</v>
       </c>
       <c r="H24" s="9">
-        <v>1.8E-3</v>
-      </c>
-      <c r="I24" s="10">
-        <v>-91.7</v>
+        <v>4.3E-3</v>
+      </c>
+      <c r="I24" s="8">
+        <v>136.69999999999999</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K24" s="9">
-        <v>9.4100000000000003E-2</v>
+        <v>4.3E-3</v>
       </c>
       <c r="L24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M24" s="9">
-        <v>1.8E-3</v>
-      </c>
-      <c r="N24" s="10">
-        <v>-91.7</v>
+        <v>4.3E-3</v>
+      </c>
+      <c r="N24" s="8">
+        <v>136.69999999999999</v>
       </c>
       <c r="O24" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P24" s="9">
-        <v>9.4100000000000003E-2</v>
+        <v>4.3E-3</v>
       </c>
       <c r="Q24" s="9" t="s">
         <v>17</v>
@@ -2448,7 +2455,7 @@
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>17</v>
@@ -2469,31 +2476,31 @@
         <v>17</v>
       </c>
       <c r="H25" s="9">
-        <v>2.1600000000000001E-2</v>
-      </c>
-      <c r="I25" s="8">
-        <v>35.9</v>
+        <v>1.8E-3</v>
+      </c>
+      <c r="I25" s="10">
+        <v>-91.7</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K25" s="9">
-        <v>9.2299999999999993E-2</v>
+        <v>9.4100000000000003E-2</v>
       </c>
       <c r="L25" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M25" s="9">
-        <v>2.1600000000000001E-2</v>
-      </c>
-      <c r="N25" s="8">
-        <v>35.9</v>
+        <v>1.8E-3</v>
+      </c>
+      <c r="N25" s="10">
+        <v>-91.7</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P25" s="9">
-        <v>9.2299999999999993E-2</v>
+        <v>9.4100000000000003E-2</v>
       </c>
       <c r="Q25" s="9" t="s">
         <v>17</v>
@@ -2501,7 +2508,7 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>17</v>
@@ -2522,31 +2529,31 @@
         <v>17</v>
       </c>
       <c r="H26" s="9">
-        <v>1.5900000000000001E-2</v>
-      </c>
-      <c r="I26" s="10">
-        <v>-20.8</v>
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="I26" s="8">
+        <v>35.9</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K26" s="9">
-        <v>7.0699999999999999E-2</v>
+        <v>9.2299999999999993E-2</v>
       </c>
       <c r="L26" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M26" s="9">
-        <v>1.5900000000000001E-2</v>
-      </c>
-      <c r="N26" s="10">
-        <v>-20.8</v>
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="N26" s="8">
+        <v>35.9</v>
       </c>
       <c r="O26" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P26" s="9">
-        <v>7.0699999999999999E-2</v>
+        <v>9.2299999999999993E-2</v>
       </c>
       <c r="Q26" s="9" t="s">
         <v>17</v>
@@ -2554,7 +2561,7 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>17</v>
@@ -2575,31 +2582,31 @@
         <v>17</v>
       </c>
       <c r="H27" s="9">
-        <v>2.01E-2</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>17</v>
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="I27" s="10">
+        <v>-20.8</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K27" s="9">
-        <v>5.4800000000000001E-2</v>
+        <v>7.0699999999999999E-2</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M27" s="9">
-        <v>2.01E-2</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>17</v>
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="N27" s="10">
+        <v>-20.8</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P27" s="9">
-        <v>5.4800000000000001E-2</v>
+        <v>7.0699999999999999E-2</v>
       </c>
       <c r="Q27" s="9" t="s">
         <v>17</v>
@@ -2607,7 +2614,7 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>17</v>
@@ -2628,31 +2635,31 @@
         <v>17</v>
       </c>
       <c r="H28" s="9">
-        <v>0</v>
-      </c>
-      <c r="I28" s="10">
-        <v>-100</v>
+        <v>2.01E-2</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K28" s="9">
-        <v>3.4700000000000002E-2</v>
+        <v>5.4800000000000001E-2</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M28" s="9">
-        <v>0</v>
-      </c>
-      <c r="N28" s="10">
-        <v>-100</v>
+        <v>2.01E-2</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O28" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P28" s="9">
-        <v>3.4700000000000002E-2</v>
+        <v>5.4800000000000001E-2</v>
       </c>
       <c r="Q28" s="9" t="s">
         <v>17</v>
@@ -2660,7 +2667,7 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>17</v>
@@ -2681,10 +2688,10 @@
         <v>17</v>
       </c>
       <c r="H29" s="9">
-        <v>3.4700000000000002E-2</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="10">
+        <v>-100</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>17</v>
@@ -2696,10 +2703,10 @@
         <v>17</v>
       </c>
       <c r="M29" s="9">
-        <v>3.4700000000000002E-2</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N29" s="10">
+        <v>-100</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>17</v>
@@ -2713,7 +2720,7 @@
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>17</v>
@@ -2734,7 +2741,7 @@
         <v>17</v>
       </c>
       <c r="H30" s="9">
-        <v>0</v>
+        <v>3.4700000000000002E-2</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>17</v>
@@ -2743,13 +2750,13 @@
         <v>17</v>
       </c>
       <c r="K30" s="9">
-        <v>0</v>
+        <v>3.4700000000000002E-2</v>
       </c>
       <c r="L30" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M30" s="9">
-        <v>0</v>
+        <v>3.4700000000000002E-2</v>
       </c>
       <c r="N30" s="9" t="s">
         <v>17</v>
@@ -2758,7 +2765,7 @@
         <v>17</v>
       </c>
       <c r="P30" s="9">
-        <v>0</v>
+        <v>3.4700000000000002E-2</v>
       </c>
       <c r="Q30" s="9" t="s">
         <v>17</v>
@@ -2766,7 +2773,7 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>17</v>
@@ -2819,7 +2826,7 @@
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>17</v>
@@ -2872,7 +2879,7 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>17</v>
@@ -2925,7 +2932,7 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>17</v>
@@ -2978,7 +2985,7 @@
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>17</v>
@@ -3031,7 +3038,7 @@
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>17</v>
@@ -3084,7 +3091,7 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>17</v>
@@ -3137,7 +3144,7 @@
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>17</v>
@@ -3190,7 +3197,7 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>17</v>
@@ -3243,7 +3250,7 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>17</v>
@@ -3296,7 +3303,7 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>17</v>
@@ -3349,7 +3356,7 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>17</v>
@@ -3402,7 +3409,7 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>17</v>
@@ -3455,7 +3462,7 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>17</v>
@@ -3508,7 +3515,7 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>17</v>
@@ -3561,7 +3568,7 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>17</v>
@@ -3614,7 +3621,7 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>17</v>
@@ -3667,7 +3674,7 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>17</v>
@@ -3720,7 +3727,7 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>17</v>
@@ -3773,7 +3780,7 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>17</v>
@@ -3826,7 +3833,7 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>17</v>
@@ -3879,7 +3886,7 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>17</v>
@@ -3932,7 +3939,7 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>17</v>
@@ -3985,7 +3992,7 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>17</v>
@@ -4038,7 +4045,7 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>17</v>
@@ -4091,7 +4098,7 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>17</v>
@@ -4144,7 +4151,7 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>17</v>
@@ -4197,7 +4204,7 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>17</v>
@@ -4250,7 +4257,7 @@
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>17</v>
@@ -4303,7 +4310,7 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>17</v>
@@ -4356,7 +4363,7 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>17</v>
@@ -4409,7 +4416,7 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>17</v>
@@ -4462,7 +4469,7 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>17</v>
@@ -4515,7 +4522,7 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>17</v>
@@ -4568,7 +4575,7 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>17</v>
@@ -4621,7 +4628,7 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>17</v>
@@ -4674,7 +4681,7 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>17</v>
@@ -4727,7 +4734,7 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>17</v>
@@ -4780,7 +4787,7 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>17</v>
@@ -4833,7 +4840,7 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>17</v>
@@ -4886,7 +4893,7 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>17</v>
@@ -4939,7 +4946,7 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>17</v>
@@ -4992,7 +4999,7 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>17</v>
@@ -5045,7 +5052,7 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>17</v>
@@ -5098,7 +5105,7 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>17</v>
@@ -5151,7 +5158,7 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>17</v>
@@ -5204,7 +5211,7 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>17</v>
@@ -5257,7 +5264,7 @@
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>17</v>
@@ -5310,7 +5317,7 @@
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>17</v>
@@ -5363,7 +5370,7 @@
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>17</v>
@@ -5416,7 +5423,7 @@
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>17</v>
@@ -5469,7 +5476,7 @@
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>17</v>
@@ -5522,54 +5529,107 @@
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
+        <v>42401</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H83" s="9">
+        <v>0</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83" s="9">
+        <v>0</v>
+      </c>
+      <c r="L83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M83" s="9">
+        <v>0</v>
+      </c>
+      <c r="N83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P83" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
         <v>42370</v>
       </c>
-      <c r="B83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H83" s="9">
-        <v>0</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K83" s="9">
-        <v>0</v>
-      </c>
-      <c r="L83" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M83" s="9">
-        <v>0</v>
-      </c>
-      <c r="N83" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O83" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P83" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="9" t="s">
+      <c r="B84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" s="9">
+        <v>0</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K84" s="9">
+        <v>0</v>
+      </c>
+      <c r="L84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M84" s="9">
+        <v>0</v>
+      </c>
+      <c r="N84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P84" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5588,7 +5648,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>